--- a/public/plantillas/plantilla-resultados-rps.xlsx
+++ b/public/plantillas/plantilla-resultados-rps.xlsx
@@ -401,7 +401,7 @@
   <dimension ref="A1:C3"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -421,7 +421,7 @@
         <v>Ana López García</v>
       </c>
       <c r="B2" t="str">
-        <v>Producción</v>
+        <v>Empresa Filial 1</v>
       </c>
       <c r="C2" t="str">
         <v>Alto</v>
@@ -432,7 +432,7 @@
         <v>Carlos Ramírez Ortiz</v>
       </c>
       <c r="B3" t="str">
-        <v>Administración</v>
+        <v>Empresa Filial 2</v>
       </c>
       <c r="C3" t="str">
         <v>Bajo</v>
@@ -447,9 +447,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <cols>
-    <col min="1" max="1" width="90.83203125" customWidth="1"/>
+    <col min="1" max="1" width="100.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,22 +474,27 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>- "NIVEL DE RIESGO" debe decir exactamente: Nulo, Bajo, Medio, Alto o Muy alto.</v>
+        <v>- "ÁREA" debe traer la empresa o razón social real a la que pertenece el trabajador (por ejemplo, si el grupo tiene varias subsidiarias, va el nombre de la subsidiaria). Ese valor se usa como "Empresa:" en el formato generado; el campo "Área:" del formato queda en blanco para llenarse a mano.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>- Solo se genera el formato de entrevista para quienes tengan "Alto" o "Muy alto".</v>
+        <v>- "NIVEL DE RIESGO" debe decir exactamente: Nulo, Bajo, Medio, Alto o Muy alto.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>- Solo se genera el formato de entrevista para quienes tengan "Alto" o "Muy alto".</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>- Borra las filas de ejemplo antes de subir tu archivo real.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/plantillas/plantilla-resultados-rps.xlsx
+++ b/public/plantillas/plantilla-resultados-rps.xlsx
@@ -398,11 +398,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B3"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -410,9 +409,6 @@
         <v>NOMBRE</v>
       </c>
       <c r="B1" t="str">
-        <v>ÁREA</v>
-      </c>
-      <c r="C1" t="str">
         <v>NIVEL DE RIESGO</v>
       </c>
     </row>
@@ -421,9 +417,6 @@
         <v>Ana López García</v>
       </c>
       <c r="B2" t="str">
-        <v>Empresa Filial 1</v>
-      </c>
-      <c r="C2" t="str">
         <v>Alto</v>
       </c>
     </row>
@@ -432,15 +425,12 @@
         <v>Carlos Ramírez Ortiz</v>
       </c>
       <c r="B3" t="str">
-        <v>Empresa Filial 2</v>
-      </c>
-      <c r="C3" t="str">
         <v>Bajo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -474,17 +464,17 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>- "ÁREA" debe traer la empresa o razón social real a la que pertenece el trabajador (por ejemplo, si el grupo tiene varias subsidiarias, va el nombre de la subsidiaria). Ese valor se usa como "Empresa:" en el formato generado; el campo "Área:" del formato queda en blanco para llenarse a mano.</v>
+        <v>- "NIVEL DE RIESGO" debe decir exactamente: Nulo, Bajo, Medio, Alto o Muy alto.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>- "NIVEL DE RIESGO" debe decir exactamente: Nulo, Bajo, Medio, Alto o Muy alto.</v>
+        <v>- Solo se genera el formato de entrevista para quienes tengan "Alto" o "Muy alto".</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>- Solo se genera el formato de entrevista para quienes tengan "Alto" o "Muy alto".</v>
+        <v>- La empresa que aparece en "Empresa:" del formato es la que está capturada en "Datos del centro de trabajo" en la app (no viene de este Excel).</v>
       </c>
     </row>
     <row r="8">
